--- a/data/trans_camb/P19C02-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P19C02-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,08; 5,2</t>
+          <t>-4,75; 5,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,68; 11,77</t>
+          <t>1,13; 11,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,79; 25,53</t>
+          <t>14,32; 26,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,29; 10,94</t>
+          <t>1,32; 11,39</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,35; 13,01</t>
+          <t>2,81; 12,72</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,88; 30,32</t>
+          <t>20,52; 30,29</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 6,98</t>
+          <t>-0,12; 7,3</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,41; 11,13</t>
+          <t>3,34; 10,89</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>19,23; 26,93</t>
+          <t>19,4; 26,4</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-20,32; 28,28</t>
+          <t>-19,14; 30,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,74; 62,91</t>
+          <t>5,11; 61,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>55,17; 135,8</t>
+          <t>56,92; 140,21</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,96; 55,51</t>
+          <t>5,24; 57,03</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,89; 66,52</t>
+          <t>10,73; 63,82</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>81,59; 153,37</t>
+          <t>79,8; 157,5</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 34,31</t>
+          <t>-0,46; 36,29</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>13,46; 54,77</t>
+          <t>13,99; 53,11</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>80,3; 136,01</t>
+          <t>81,2; 133,25</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 8,15</t>
+          <t>-1,37; 7,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,4; 15,23</t>
+          <t>5,37; 14,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,46; 25,76</t>
+          <t>-6,44; 25,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,36; 2,77</t>
+          <t>-6,52; 2,39</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,24; 14,91</t>
+          <t>5,02; 14,36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19,16; 27,73</t>
+          <t>19,01; 27,37</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 3,71</t>
+          <t>-2,39; 3,77</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,63; 13,33</t>
+          <t>6,46; 13,37</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,11; 24,27</t>
+          <t>-0,27; 24,48</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 34,17</t>
+          <t>-4,58; 30,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18,12; 63,47</t>
+          <t>17,91; 59,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-25,96; 100,13</t>
+          <t>-20,14; 101,56</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-20,79; 10,31</t>
+          <t>-21,72; 9,14</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>16,92; 56,78</t>
+          <t>16,48; 55,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,79; 106,4</t>
+          <t>61,42; 105,75</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-8,86; 14,16</t>
+          <t>-8,16; 14,63</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>22,37; 50,84</t>
+          <t>22,23; 51,17</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,05; 89,71</t>
+          <t>-0,58; 89,91</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,21; 4,09</t>
+          <t>-7,0; 4,11</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 8,72</t>
+          <t>-2,75; 8,76</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,44; 19,89</t>
+          <t>7,49; 19,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,99; 5,73</t>
+          <t>-5,16; 5,75</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,97; 12,26</t>
+          <t>0,74; 12,23</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,45; 43,29</t>
+          <t>4,24; 42,68</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 3,29</t>
+          <t>-4,1; 3,97</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,66; 8,79</t>
+          <t>1,33; 8,84</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,66; 39,17</t>
+          <t>8,75; 38,45</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-21,64; 14,75</t>
+          <t>-21,65; 15,43</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-8,92; 32,19</t>
+          <t>-8,69; 31,4</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>22,4; 71,93</t>
+          <t>22,76; 73,52</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-14,32; 18,56</t>
+          <t>-14,3; 18,05</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,55; 40,18</t>
+          <t>2,11; 39,49</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12,75; 136,28</t>
+          <t>12,55; 131,96</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-13,27; 10,65</t>
+          <t>-12,23; 13,22</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,45; 30,16</t>
+          <t>3,85; 29,4</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>25,96; 124,75</t>
+          <t>26,77; 126,77</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 6,77</t>
+          <t>-3,06; 6,52</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 8,84</t>
+          <t>-0,78; 9,31</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10,18; 20,12</t>
+          <t>10,26; 20,13</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 9,11</t>
+          <t>-0,05; 9,48</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,94; 12,05</t>
+          <t>2,39; 11,75</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,56; 20,6</t>
+          <t>5,31; 20,02</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 6,5</t>
+          <t>-0,05; 6,65</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,8; 9,55</t>
+          <t>2,5; 9,46</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9,06; 18,65</t>
+          <t>9,43; 18,78</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-9,16; 21,6</t>
+          <t>-8,57; 20,81</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 28,8</t>
+          <t>-1,78; 29,73</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>27,24; 63,89</t>
+          <t>28,54; 65,28</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 32,06</t>
+          <t>0,04; 33,36</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8,68; 42,26</t>
+          <t>6,87; 41,75</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,27; 71,96</t>
+          <t>18,8; 69,35</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 21,37</t>
+          <t>-0,35; 21,52</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>8,25; 31,06</t>
+          <t>7,39; 31,17</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>27,38; 60,24</t>
+          <t>28,51; 61,17</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 3,66</t>
+          <t>-1,25; 3,78</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,48; 8,79</t>
+          <t>3,42; 8,65</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5,72; 19,28</t>
+          <t>5,34; 19,18</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 4,61</t>
+          <t>-0,6; 4,48</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,48; 10,66</t>
+          <t>5,33; 10,55</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>16,34; 30,13</t>
+          <t>16,6; 29,82</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 3,22</t>
+          <t>-0,24; 3,34</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>5,2; 8,92</t>
+          <t>5,53; 9,17</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>12,9; 22,36</t>
+          <t>12,78; 22,28</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 13,47</t>
+          <t>-4,28; 13,91</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>11,52; 32,0</t>
+          <t>11,37; 31,2</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>20,64; 69,24</t>
+          <t>19,64; 68,68</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 16,85</t>
+          <t>-2,01; 16,04</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>18,18; 38,44</t>
+          <t>17,51; 38,09</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>54,66; 105,87</t>
+          <t>55,69; 103,71</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 11,66</t>
+          <t>-0,71; 12,05</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>17,38; 31,98</t>
+          <t>18,32; 32,88</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>44,04; 79,34</t>
+          <t>43,93; 79,59</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P19C02-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P19C02-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20,17</t>
+          <t>21,32</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,79</t>
+          <t>26,47</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>23,06</t>
+          <t>23,98</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 5,55</t>
+          <t>-5,33; 5,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,13; 11,92</t>
+          <t>0,8; 11,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,32; 26,0</t>
+          <t>14,77; 26,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,32; 11,39</t>
+          <t>1,23; 11,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,81; 12,72</t>
+          <t>2,36; 12,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,52; 30,29</t>
+          <t>21,75; 31,12</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 7,3</t>
+          <t>-0,4; 6,75</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,34; 10,89</t>
+          <t>3,17; 10,86</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>19,4; 26,4</t>
+          <t>20,21; 27,58</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>115,15%</t>
+          <t>118,19%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>104,61%</t>
+          <t>108,77%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-19,14; 30,1</t>
+          <t>-21,42; 27,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,11; 61,26</t>
+          <t>3,01; 62,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>56,92; 140,21</t>
+          <t>61,06; 139,62</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,24; 57,03</t>
+          <t>4,4; 55,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,73; 63,82</t>
+          <t>9,67; 66,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>79,8; 157,5</t>
+          <t>84,94; 162,37</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 36,29</t>
+          <t>-1,68; 33,74</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>13,99; 53,11</t>
+          <t>12,77; 55,34</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>81,2; 133,25</t>
+          <t>82,15; 137,79</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>13,18</t>
+          <t>24,2</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>23,16</t>
+          <t>23,57</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>17,51</t>
+          <t>23,85</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 7,56</t>
+          <t>-1,43; 8,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,37; 14,81</t>
+          <t>4,94; 15,01</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,44; 25,86</t>
+          <t>19,08; 29,6</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,52; 2,39</t>
+          <t>-6,55; 2,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,02; 14,36</t>
+          <t>4,95; 14,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19,01; 27,37</t>
+          <t>19,13; 27,88</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 3,77</t>
+          <t>-2,77; 3,79</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,46; 13,37</t>
+          <t>6,26; 13,04</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 24,48</t>
+          <t>20,86; 27,37</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>48,96%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>81,34%</t>
+          <t>82,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>63,14%</t>
+          <t>86,0%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,58; 30,9</t>
+          <t>-4,85; 33,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,91; 59,73</t>
+          <t>16,27; 60,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-20,14; 101,56</t>
+          <t>63,03; 120,78</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-21,72; 9,14</t>
+          <t>-21,54; 8,51</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>16,48; 55,25</t>
+          <t>16,03; 54,77</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,42; 105,75</t>
+          <t>62,23; 110,63</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-8,16; 14,63</t>
+          <t>-9,43; 14,59</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>22,23; 51,17</t>
+          <t>20,98; 50,22</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 89,91</t>
+          <t>70,12; 106,82</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13,85</t>
+          <t>13,32</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19,82</t>
+          <t>9,26</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>17,46</t>
+          <t>11,23</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,0; 4,11</t>
+          <t>-7,08; 4,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 8,76</t>
+          <t>-3,53; 8,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,49; 19,95</t>
+          <t>7,39; 19,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 5,75</t>
+          <t>-4,62; 5,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,74; 12,23</t>
+          <t>0,89; 12,23</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,24; 42,68</t>
+          <t>4,49; 14,32</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 3,97</t>
+          <t>-4,74; 3,34</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,33; 8,84</t>
+          <t>1,13; 9,07</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,75; 38,45</t>
+          <t>7,02; 14,93</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>44,21%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,13%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>54,77%</t>
+          <t>35,22%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-21,65; 15,43</t>
+          <t>-21,4; 15,45</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-8,69; 31,4</t>
+          <t>-10,6; 32,08</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>22,76; 73,52</t>
+          <t>22,71; 69,85</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-14,3; 18,05</t>
+          <t>-13,08; 20,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,11; 39,49</t>
+          <t>2,58; 39,31</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12,55; 131,96</t>
+          <t>12,27; 46,96</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-12,23; 13,22</t>
+          <t>-13,92; 11,14</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,85; 29,4</t>
+          <t>3,47; 30,34</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>26,77; 126,77</t>
+          <t>20,67; 50,25</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15,06</t>
+          <t>14,98</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,1</t>
+          <t>18,52</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>15,05</t>
+          <t>16,87</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 6,52</t>
+          <t>-2,93; 7,19</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 9,31</t>
+          <t>-1,06; 9,17</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10,26; 20,13</t>
+          <t>9,96; 20,61</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 9,48</t>
+          <t>0,01; 8,43</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,39; 11,75</t>
+          <t>3,1; 12,32</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,31; 20,02</t>
+          <t>14,2; 22,39</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 6,65</t>
+          <t>0,17; 6,67</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,5; 9,46</t>
+          <t>2,79; 9,7</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9,43; 18,78</t>
+          <t>13,45; 20,12</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>44,46%</t>
+          <t>44,22%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>48,71%</t>
+          <t>59,77%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>46,55%</t>
+          <t>52,17%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-8,57; 20,81</t>
+          <t>-7,98; 23,35</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 29,73</t>
+          <t>-2,01; 29,84</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>28,54; 65,28</t>
+          <t>27,39; 67,01</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,04; 33,36</t>
+          <t>0,34; 29,78</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,87; 41,75</t>
+          <t>8,66; 42,63</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,8; 69,35</t>
+          <t>41,85; 79,33</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 21,52</t>
+          <t>0,53; 21,76</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>7,39; 31,17</t>
+          <t>8,22; 31,9</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>28,51; 61,17</t>
+          <t>38,95; 66,3</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>14,93</t>
+          <t>18,54</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>20,69</t>
+          <t>19,54</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>17,9</t>
+          <t>19,05</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 3,78</t>
+          <t>-1,63; 3,79</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,42; 8,65</t>
+          <t>3,35; 8,8</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5,34; 19,18</t>
+          <t>15,74; 21,04</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 4,48</t>
+          <t>-0,52; 4,34</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,33; 10,55</t>
+          <t>5,44; 10,47</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>16,6; 29,82</t>
+          <t>17,29; 21,79</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 3,34</t>
+          <t>-0,07; 3,45</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>5,53; 9,17</t>
+          <t>5,44; 9,08</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>12,78; 22,28</t>
+          <t>17,19; 20,7</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>52,19%</t>
+          <t>64,79%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>71,1%</t>
+          <t>67,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>62,0%</t>
+          <t>65,98%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 13,91</t>
+          <t>-5,43; 14,0</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>11,37; 31,2</t>
+          <t>11,23; 32,68</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>19,64; 68,68</t>
+          <t>51,99; 77,5</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 16,04</t>
+          <t>-1,7; 15,54</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>17,51; 38,09</t>
+          <t>18,08; 37,38</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>55,69; 103,71</t>
+          <t>55,9; 78,71</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 12,05</t>
+          <t>-0,25; 12,28</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>18,32; 32,88</t>
+          <t>18,37; 32,8</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>43,93; 79,59</t>
+          <t>57,68; 74,06</t>
         </is>
       </c>
     </row>
